--- a/tests/workbooktests/workbooks/test_swap.xlsx
+++ b/tests/workbooktests/workbooks/test_swap.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C6075C-3C0A-481D-A5B8-661ED09392D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939CAC17-0599-4E39-975F-6DA80627BBD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{A576409D-E527-4FE8-BADF-F8DE357B9837}"/>
+    <workbookView xWindow="3885" yWindow="-18240" windowWidth="30690" windowHeight="16530" activeTab="1" xr2:uid="{A576409D-E527-4FE8-BADF-F8DE357B9837}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabs" sheetId="1" r:id="rId1"/>
@@ -47,6 +47,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1107,7 +1129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1187,6 +1209,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1200,9 +1244,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1533,7 +1574,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="47" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="29"/>
@@ -1545,7 +1586,7 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="40"/>
+      <c r="B3" s="48"/>
       <c r="C3" s="31"/>
       <c r="D3" s="31"/>
       <c r="E3" s="32" t="s">
@@ -1927,11 +1968,11 @@
         <v>174</v>
       </c>
       <c r="B10" s="9" t="str">
-        <f>_xll.qlEuribor("12M",B9)</f>
+        <f>_xll.qlEuribor("12M",B9,B2)</f>
         <v>欣[test_swap.xlsx]ZeroCouponSwap!R10C2Euribor,A</v>
       </c>
       <c r="C10" s="9" t="str">
-        <f>_xll.qlEuribor("12M",C9)</f>
+        <f>_xll.qlEuribor("12M",C9,B2)</f>
         <v>欣[test_swap.xlsx]ZeroCouponSwap!R10C3Euribor,A</v>
       </c>
     </row>
@@ -2128,8 +2169,8 @@
         <f>_xll.qlSwapNpvDateDiscount(B14,B17)</f>
         <v>1</v>
       </c>
-      <c r="C26" s="9">
-        <f>_xll.qlSwapNpvDateDiscount(C14)</f>
+      <c r="C26" s="44">
+        <f>_xll.qlSwapNpvDateDiscount(C14,C17)</f>
         <v>1</v>
       </c>
     </row>
@@ -2229,11 +2270,11 @@
         <v>183</v>
       </c>
       <c r="B34" s="9">
-        <f>_xll.qlZeroCouponSwapFixedLegNPV(B14)</f>
+        <f>_xll.qlZeroCouponSwapFixedLegNPV(B14,B17)</f>
         <v>-4.8506326770153034</v>
       </c>
-      <c r="C34" s="37">
-        <f>_xll.qlZeroCouponSwapFixedLegNPV(C14)</f>
+      <c r="C34" s="46">
+        <f>_xll.qlZeroCouponSwapFixedLegNPV(C14,C17)</f>
         <v>-4.8506326770153034</v>
       </c>
     </row>
@@ -2360,11 +2401,11 @@
         <v>174</v>
       </c>
       <c r="B48" s="9" t="str">
-        <f>_xll.qlEuribor("12M",B47)</f>
+        <f>_xll.qlEuribor("12M",B47,B2)</f>
         <v>欣[test_swap.xlsx]ZeroCouponSwap!R48C2Euribor,A</v>
       </c>
       <c r="C48" s="9" t="str">
-        <f>_xll.qlEuribor("12M",C47)</f>
+        <f>_xll.qlEuribor("12M",C47,B2)</f>
         <v>欣[test_swap.xlsx]ZeroCouponSwap!R48C3Euribor,A</v>
       </c>
     </row>
@@ -2945,11 +2986,11 @@
         <v>190</v>
       </c>
       <c r="B21" s="9" t="str">
-        <f>_xll.qlEuribor("12M",B20)</f>
+        <f>_xll.qlEuribor("12M",B20,B2)</f>
         <v>欣[test_swap.xlsx]EquityTotalReturnSwap!R21C2Euribor,A</v>
       </c>
       <c r="C21" s="9" t="str">
-        <f>_xll.qlEuribor("12M",C20)</f>
+        <f>_xll.qlEuribor("12M",C20,B2)</f>
         <v>欣[test_swap.xlsx]EquityTotalReturnSwap!R21C3Euribor,A</v>
       </c>
     </row>
@@ -4086,7 +4127,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="4" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>26</v>
       </c>
@@ -4094,7 +4135,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>27</v>
       </c>
@@ -4102,7 +4143,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>28</v>
       </c>
@@ -4110,7 +4151,7 @@
         <v>46395</v>
       </c>
     </row>
-    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>29</v>
       </c>
@@ -4118,7 +4159,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>30</v>
       </c>
@@ -4126,7 +4167,7 @@
         <v>45816</v>
       </c>
     </row>
-    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>31</v>
       </c>
@@ -4134,7 +4175,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>32</v>
       </c>
@@ -4142,7 +4183,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="11" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>33</v>
       </c>
@@ -4150,7 +4191,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>34</v>
       </c>
@@ -4158,7 +4199,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>35</v>
       </c>
@@ -4166,7 +4207,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="14" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>36</v>
       </c>
@@ -4174,7 +4215,7 @@
         <v>46395</v>
       </c>
     </row>
-    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>37</v>
       </c>
@@ -4183,7 +4224,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="41" t="s">
+      <c r="A16" s="49" t="s">
         <v>38</v>
       </c>
       <c r="B16" s="9" t="str">
@@ -4192,14 +4233,14 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="41"/>
+      <c r="A17" s="49"/>
       <c r="B17" s="9" t="str">
         <f>_xll.qlSimpleCashFlow(B7,B6)</f>
         <v>欣[test_swap.xlsx]Swap!R17C2SimpleCashFlow,A</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="49" t="s">
         <v>39</v>
       </c>
       <c r="B18" s="9" t="str">
@@ -4208,21 +4249,21 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="41"/>
+      <c r="A19" s="49"/>
       <c r="B19" s="9" t="str">
         <f>_xll.qlSimpleCashFlow(B11,B10)</f>
         <v>欣[test_swap.xlsx]Swap!R19C2SimpleCashFlow,A</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="41"/>
+      <c r="A20" s="49"/>
       <c r="B20" s="9" t="str">
         <f>_xll.qlSimpleCashFlow(B13,B12)</f>
         <v>欣[test_swap.xlsx]Swap!R20C2SimpleCashFlow,A</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="41"/>
+      <c r="A21" s="49"/>
       <c r="B21" s="9" t="str">
         <f>_xll.qlSimpleCashFlow(B15,B14)</f>
         <v>欣[test_swap.xlsx]Swap!R21C2SimpleCashFlow,A</v>
@@ -4266,7 +4307,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="9" t="str">
-        <f>_xll.qlDiscountingSwapEngine(B23)</f>
+        <f>_xll.qlDiscountingSwapEngine(B23,B2)</f>
         <v>欣[test_swap.xlsx]Swap!R27C2DiscountingSwapEngine,A</v>
       </c>
     </row>
@@ -4356,7 +4397,7 @@
         <v>20</v>
       </c>
       <c r="B37" s="9">
-        <f>_xll.qlSwapNpvDateDiscount(B22)</f>
+        <f>_xll.qlSwapNpvDateDiscount(B22,B28)</f>
         <v>1</v>
       </c>
     </row>
@@ -4427,7 +4468,7 @@
       </c>
     </row>
     <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="43" t="s">
+      <c r="A49" s="51" t="s">
         <v>51</v>
       </c>
       <c r="B49" s="33">
@@ -4438,7 +4479,7 @@
       <c r="E49" s="24"/>
     </row>
     <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="43"/>
+      <c r="A50" s="51"/>
       <c r="B50" s="33">
         <f>B49+1</f>
         <v>101</v>
@@ -4448,7 +4489,7 @@
       <c r="E50" s="24"/>
     </row>
     <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="43"/>
+      <c r="A51" s="51"/>
       <c r="B51" s="33">
         <f t="shared" ref="B51:B55" si="0">B50+1</f>
         <v>102</v>
@@ -4458,7 +4499,7 @@
       <c r="E51" s="24"/>
     </row>
     <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="43"/>
+      <c r="A52" s="51"/>
       <c r="B52" s="33">
         <f t="shared" si="0"/>
         <v>103</v>
@@ -4468,7 +4509,7 @@
       <c r="E52" s="24"/>
     </row>
     <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="43"/>
+      <c r="A53" s="51"/>
       <c r="B53" s="33">
         <f t="shared" si="0"/>
         <v>104</v>
@@ -4478,7 +4519,7 @@
       <c r="E53" s="24"/>
     </row>
     <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="43"/>
+      <c r="A54" s="51"/>
       <c r="B54" s="33">
         <f t="shared" si="0"/>
         <v>105</v>
@@ -4488,7 +4529,7 @@
       <c r="E54" s="24"/>
     </row>
     <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="43"/>
+      <c r="A55" s="51"/>
       <c r="B55" s="33">
         <f t="shared" si="0"/>
         <v>106</v>
@@ -4498,7 +4539,7 @@
       <c r="E55" s="24"/>
     </row>
     <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="43"/>
+      <c r="A56" s="51"/>
       <c r="B56" s="9">
         <f>B55+1</f>
         <v>107</v>
@@ -4508,7 +4549,7 @@
       <c r="E56" s="24"/>
     </row>
     <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="43" t="s">
+      <c r="A57" s="51" t="s">
         <v>52</v>
       </c>
       <c r="B57" s="33">
@@ -4519,7 +4560,7 @@
       <c r="E57" s="24"/>
     </row>
     <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="43"/>
+      <c r="A58" s="51"/>
       <c r="B58" s="33">
         <v>0.02</v>
       </c>
@@ -4550,7 +4591,7 @@
         <v>54</v>
       </c>
       <c r="B61" s="9" t="str">
-        <f>_xll.qlEuribor("3m",B60)</f>
+        <f>_xll.qlEuribor("3m",B60,B2)</f>
         <v>欣[test_swap.xlsx]Swap!R61C2Euribor,A</v>
       </c>
     </row>
@@ -4564,7 +4605,7 @@
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="42" t="s">
+      <c r="A63" s="50" t="s">
         <v>57</v>
       </c>
       <c r="B63" s="9" t="str">
@@ -4573,14 +4614,14 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="42"/>
+      <c r="A64" s="50"/>
       <c r="B64" s="9" t="str">
         <f>_xll.qlIborLeg(B49,B47,B61)</f>
         <v>欣[test_swap.xlsx]Swap!R64C2CashFlow,A</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="41" t="s">
+      <c r="A65" s="49" t="s">
         <v>58</v>
       </c>
       <c r="B65" s="9" t="b">
@@ -4588,7 +4629,7 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="41"/>
+      <c r="A66" s="49"/>
       <c r="B66" s="9" t="b">
         <v>1</v>
       </c>
@@ -4637,7 +4678,7 @@
         <v>21</v>
       </c>
       <c r="B72" s="9" t="str">
-        <f>_xll.qlDiscountingSwapEngine(B68)</f>
+        <f>_xll.qlDiscountingSwapEngine(B68,B2)</f>
         <v>欣[test_swap.xlsx]Swap!R72C2DiscountingSwapEngine,A</v>
       </c>
     </row>
@@ -4727,7 +4768,7 @@
         <v>20</v>
       </c>
       <c r="B82" s="9">
-        <f>_xll.qlSwapNpvDateDiscount(B67)</f>
+        <f>_xll.qlSwapNpvDateDiscount(B67,B73)</f>
         <v>1</v>
       </c>
     </row>
@@ -4980,11 +5021,11 @@
         <v>66</v>
       </c>
       <c r="B21" s="8" t="str">
-        <f>_xll.qlEuribor("3m",B20)</f>
-        <v>欣[test_swap.xlsx]VanillaSwap!R21C2Euribor,A</v>
+        <f>_xll.qlEuribor("3m",B20,B2)</f>
+        <v>欣[test_swap.xlsx]VanillaSwap!R21C2Euribor,G</v>
       </c>
       <c r="C21" s="8" t="str">
-        <f>_xll.qlEuribor("3m",C20)</f>
+        <f>_xll.qlEuribor("3m",C20,B2)</f>
         <v>欣[test_swap.xlsx]VanillaSwap!R21C3Euribor,A</v>
       </c>
     </row>
@@ -5571,11 +5612,11 @@
         <v>174</v>
       </c>
       <c r="B6" s="11" t="str">
-        <f>_xll.qlEuribor("3M",B5)</f>
+        <f>_xll.qlEuribor("3M",B5,B2)</f>
         <v>欣[test_swap.xlsx]MakeVanillaSwap!R6C2Euribor,A</v>
       </c>
       <c r="C6" s="11" t="str">
-        <f>_xll.qlEuribor("3M",C5)</f>
+        <f>_xll.qlEuribor("3M",C5,B2)</f>
         <v>欣[test_swap.xlsx]MakeVanillaSwap!R6C3Euribor,A</v>
       </c>
     </row>
@@ -6298,11 +6339,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF6E3443-1F61-4CD4-9E60-3D9682C914F4}">
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.88671875" customWidth="1"/>
     <col min="2" max="3" width="64.33203125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -6334,7 +6376,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="49" t="s">
         <v>76</v>
       </c>
       <c r="B5" s="8">
@@ -6345,7 +6387,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="41"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="8">
         <v>110</v>
       </c>
@@ -6354,7 +6396,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="41"/>
+      <c r="A7" s="49"/>
       <c r="B7" s="8">
         <v>120</v>
       </c>
@@ -6363,7 +6405,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="49" t="s">
         <v>77</v>
       </c>
       <c r="B8" s="8">
@@ -6374,7 +6416,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="41"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="8">
         <v>210</v>
       </c>
@@ -6383,7 +6425,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="41"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="8">
         <v>220</v>
       </c>
@@ -6461,7 +6503,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="49" t="s">
         <v>63</v>
       </c>
       <c r="B17" s="8">
@@ -6472,7 +6514,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="41"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="8">
         <v>3.3000000000000002E-2</v>
       </c>
@@ -6481,7 +6523,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="41"/>
+      <c r="A19" s="49"/>
       <c r="B19" s="8">
         <v>3.5999999999999997E-2</v>
       </c>
@@ -6586,16 +6628,16 @@
         <v>66</v>
       </c>
       <c r="B28" s="8" t="str">
-        <f>_xll.qlEuribor("3m",B27)</f>
+        <f>_xll.qlEuribor("3m",B27,B2)</f>
         <v>欣[test_swap.xlsx]NonStandardSwap!R28C2Euribor,A</v>
       </c>
       <c r="C28" s="8" t="str">
-        <f>_xll.qlEuribor("3m",C27)</f>
+        <f>_xll.qlEuribor("3m",C27,B2)</f>
         <v>欣[test_swap.xlsx]NonStandardSwap!R28C3Euribor,A</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="41" t="s">
+      <c r="A29" s="49" t="s">
         <v>78</v>
       </c>
       <c r="B29" s="8">
@@ -6606,7 +6648,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="41"/>
+      <c r="A30" s="49"/>
       <c r="B30" s="8">
         <v>1</v>
       </c>
@@ -6615,7 +6657,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="41"/>
+      <c r="A31" s="49"/>
       <c r="B31" s="8">
         <v>2</v>
       </c>
@@ -6624,7 +6666,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="41" t="s">
+      <c r="A32" s="49" t="s">
         <v>67</v>
       </c>
       <c r="B32" s="8">
@@ -6635,7 +6677,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="41"/>
+      <c r="A33" s="49"/>
       <c r="B33" s="8">
         <v>2E-3</v>
       </c>
@@ -6644,7 +6686,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="41"/>
+      <c r="A34" s="49"/>
       <c r="B34" s="8">
         <v>3.0000000000000001E-3</v>
       </c>
@@ -6910,20 +6952,20 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="44" t="s">
+      <c r="A57" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="39" cm="1">
         <f t="array" ref="B57:B59">_xll.qlNonstandardSwapFixedNominal(B39)</f>
         <v>100</v>
       </c>
-      <c r="C57" s="8">
-        <f t="array" ref="C57:C59">_xll.qlNonstandardSwapFixedNominal(C39)</f>
+      <c r="C57" s="39" cm="1">
+        <f t="array" ref="C57:C62">_xll.qlNonstandardSwapFixedNominal(C39)</f>
         <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="44"/>
+      <c r="A58" s="42"/>
       <c r="B58" s="8">
         <v>110</v>
       </c>
@@ -6932,7 +6974,7 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="44"/>
+      <c r="A59" s="42"/>
       <c r="B59" s="8">
         <v>120</v>
       </c>
@@ -6941,307 +6983,329 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="44" t="s">
+      <c r="A60" s="40"/>
+      <c r="B60" s="39"/>
+      <c r="C60" s="39">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="40"/>
+      <c r="B61" s="39"/>
+      <c r="C61" s="39">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="40"/>
+      <c r="B62" s="39"/>
+      <c r="C62" s="39">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="B60" s="8">
-        <f t="array" ref="B60:B62">_xll.qlNonstandardSwapFloatingNominal(B39)</f>
+      <c r="B63" s="39" cm="1">
+        <f t="array" ref="B63:B65">_xll.qlNonstandardSwapFloatingNominal(B39)</f>
         <v>200</v>
       </c>
-      <c r="C60" s="8">
-        <f t="array" ref="C60:C62">_xll.qlNonstandardSwapFloatingNominal(C39)</f>
+      <c r="C63" s="39" cm="1">
+        <f t="array" ref="C63:C68">_xll.qlNonstandardSwapFloatingNominal(C39)</f>
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="44"/>
-      <c r="B61" s="8">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="42"/>
+      <c r="B64" s="8">
         <v>210</v>
       </c>
-      <c r="C61" s="8">
+      <c r="C64" s="8">
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="44"/>
-      <c r="B62" s="8">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="42"/>
+      <c r="B65" s="8">
         <v>220</v>
       </c>
-      <c r="C62" s="8">
+      <c r="C65" s="8">
         <v>210</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="42"/>
+      <c r="B66" s="39"/>
+      <c r="C66" s="39">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="42"/>
+      <c r="B67" s="39"/>
+      <c r="C67" s="39">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="42"/>
+      <c r="B68" s="39"/>
+      <c r="C68" s="39">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B63" s="8" t="str">
+      <c r="B69" s="8" t="str">
         <f xml:space="preserve"> _xll.qlNonstandardSwapFixedSchedule(B39)</f>
-        <v>欣[test_swap.xlsx]NonStandardSwap!R63C2Schedule,A</v>
-      </c>
-      <c r="C63" s="8" t="str">
+        <v>欣[test_swap.xlsx]NonStandardSwap!R69C2Schedule,A</v>
+      </c>
+      <c r="C69" s="8" t="str">
         <f xml:space="preserve"> _xll.qlNonstandardSwapFixedSchedule(C39)</f>
-        <v>欣[test_swap.xlsx]NonStandardSwap!R63C3Schedule,A</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="44" t="s">
+        <v>欣[test_swap.xlsx]NonStandardSwap!R69C3Schedule,A</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="B64" s="8">
-        <f t="array" ref="B64:B66">_xll.qlNonstandardSwapFixedRate(B39)</f>
+      <c r="B70" s="41" cm="1">
+        <f t="array" ref="B70:B72">_xll.qlNonstandardSwapFixedRate(B39)</f>
         <v>0.03</v>
       </c>
-      <c r="C64" s="8">
-        <f t="array" ref="C64:C66">_xll.qlNonstandardSwapFixedRate(C39)</f>
+      <c r="C70" s="41" cm="1">
+        <f t="array" ref="C70:C75">_xll.qlNonstandardSwapFixedRate(C39)</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="44"/>
-      <c r="B65" s="8">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="42"/>
+      <c r="B71" s="8">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="C65" s="8">
+      <c r="C71" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="44"/>
-      <c r="B66" s="8">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="42"/>
+      <c r="B72" s="8">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="C66" s="8">
+      <c r="C72" s="8">
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="42"/>
+      <c r="B73" s="41"/>
+      <c r="C73" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="42"/>
+      <c r="B74" s="41"/>
+      <c r="C74" s="41">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="42"/>
+      <c r="B75" s="41"/>
+      <c r="C75" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B67" s="8" t="str">
+      <c r="B76" s="8" t="str">
         <f>_xll.qlNonstandardSwapFixedDayCount(B39)</f>
         <v>Actual/365 (Fixed)</v>
       </c>
-      <c r="C67" s="8" t="str">
+      <c r="C76" s="8" t="str">
         <f>_xll.qlNonstandardSwapFixedDayCount(C39)</f>
         <v>Actual/365 (Fixed)</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B68" s="8" t="str">
+      <c r="B77" s="8" t="str">
         <f xml:space="preserve"> _xll.qlNonstandardSwapFloatingSchedule(B39)</f>
-        <v>欣[test_swap.xlsx]NonStandardSwap!R68C2Schedule,A</v>
-      </c>
-      <c r="C68" s="8" t="str">
+        <v>欣[test_swap.xlsx]NonStandardSwap!R77C2Schedule,A</v>
+      </c>
+      <c r="C77" s="8" t="str">
         <f xml:space="preserve"> _xll.qlNonstandardSwapFloatingSchedule(C39)</f>
-        <v>欣[test_swap.xlsx]NonStandardSwap!R68C3Schedule,A</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B69" s="8" t="str">
-        <f>_xll.qlNonstandardSwapIborIndex(B39)</f>
-        <v>欣[test_swap.xlsx]NonStandardSwap!R69C2IborIndex,A</v>
-      </c>
-      <c r="C69" s="8" t="str">
-        <f>_xll.qlNonstandardSwapIborIndex(C39)</f>
-        <v>欣[test_swap.xlsx]NonStandardSwap!R69C3IborIndex,A</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B70" s="8" t="str">
-        <f>_xll.qlNonstandardSwapSpread(B39)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: spread is a vector, use spreads inspector instead
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\swap.py", line 916, in qlNonstandardSwapSpread
-    return swap.spread()
-           ~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 22519, in spread
-    return _QuantLib.NonstandardSwap_spread(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: spread is a vector, use spreads inspector instead
-</v>
-      </c>
-      <c r="C70" s="8" t="str">
-        <f>_xll.qlNonstandardSwapSpread(C39)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: spread is a vector, use spreads inspector instead
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\swap.py", line 916, in qlNonstandardSwapSpread
-    return swap.spread()
-           ~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 22519, in spread
-    return _QuantLib.NonstandardSwap_spread(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: spread is a vector, use spreads inspector instead
-</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B71" s="8" t="str">
-        <f>_xll.qlNonstandardSwapGearing(B39)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: gearing is a vector, use gearings inspector instead
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\swap.py", line 927, in qlNonstandardSwapGearing
-    return swap.gearing()
-           ~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 22523, in gearing
-    return _QuantLib.NonstandardSwap_gearing(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: gearing is a vector, use gearings inspector instead
-</v>
-      </c>
-      <c r="C71" s="8" t="str">
-        <f>_xll.qlNonstandardSwapGearing(C39)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: gearing is a vector, use gearings inspector instead
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\swap.py", line 927, in qlNonstandardSwapGearing
-    return swap.gearing()
-           ~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 22523, in gearing
-    return _QuantLib.NonstandardSwap_gearing(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: gearing is a vector, use gearings inspector instead
-</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="B72" s="8">
-        <f t="array" ref="B72:B74">_xll.qlNonstandardSwapSpreads(B39)</f>
-        <v>1E-3</v>
-      </c>
-      <c r="C72" s="8">
-        <f t="array" ref="C72:C74">_xll.qlNonstandardSwapSpreads(C39)</f>
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="44"/>
-      <c r="B73" s="8">
-        <v>2E-3</v>
-      </c>
-      <c r="C73" s="8">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="44"/>
-      <c r="B74" s="8">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="C74" s="8">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="B75" s="8">
-        <f t="array" ref="B75:B77">_xll.qlNonstandardSwapGearings(B39)</f>
-        <v>2.2204460492503131E-16</v>
-      </c>
-      <c r="C75" s="8">
-        <f t="array" ref="C75:C77">_xll.qlNonstandardSwapGearings(C39)</f>
-        <v>2.2204460492503131E-16</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="44"/>
-      <c r="B76" s="8">
-        <v>1</v>
-      </c>
-      <c r="C76" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="44"/>
-      <c r="B77" s="8">
-        <v>2</v>
-      </c>
-      <c r="C77" s="8">
-        <v>2</v>
+        <v>欣[test_swap.xlsx]NonStandardSwap!R77C3Schedule,A</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B78" s="8" t="str">
+        <f>_xll.qlNonstandardSwapIborIndex(B39)</f>
+        <v>欣[test_swap.xlsx]NonStandardSwap!R78C2IborIndex,A</v>
+      </c>
+      <c r="C78" s="8" t="str">
+        <f>_xll.qlNonstandardSwapIborIndex(C39)</f>
+        <v>欣[test_swap.xlsx]NonStandardSwap!R78C3IborIndex,A</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B79" s="43">
+        <f>FIND("RuntimeError: RuntimeError: spread is a vector, use spreads inspector instead",_xll.qlNonstandardSwapSpread(B39))</f>
+        <v>1</v>
+      </c>
+      <c r="C79" s="43">
+        <f>FIND("RuntimeError: RuntimeError: spread is a vector, use spreads inspector instead",_xll.qlNonstandardSwapSpread(C39))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B80" s="43">
+        <f>FIND("RuntimeError: RuntimeError: gearing is a vector, use gearings inspector instead",_xll.qlNonstandardSwapGearing(B39))</f>
+        <v>1</v>
+      </c>
+      <c r="C80" s="43">
+        <f>FIND("RuntimeError: RuntimeError: gearing is a vector, use gearings inspector instead",_xll.qlNonstandardSwapGearing(C39))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="B81" s="39" cm="1">
+        <f t="array" ref="B81:B83">_xll.qlNonstandardSwapSpreads(B39)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="C81" s="39" cm="1">
+        <f t="array" ref="C81:C83">_xll.qlNonstandardSwapSpreads(C39)</f>
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="42"/>
+      <c r="B82" s="8">
+        <v>2E-3</v>
+      </c>
+      <c r="C82" s="8">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="42"/>
+      <c r="B83" s="8">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C83" s="8">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="B84" s="41" cm="1">
+        <f t="array" ref="B84:B86">_xll.qlNonstandardSwapGearings(B39)</f>
+        <v>2.2204460492503131E-16</v>
+      </c>
+      <c r="C84" s="41" cm="1">
+        <f t="array" ref="C84:C86">_xll.qlNonstandardSwapGearings(C39)</f>
+        <v>2.2204460492503131E-16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="42"/>
+      <c r="B85" s="8">
+        <v>1</v>
+      </c>
+      <c r="C85" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="42"/>
+      <c r="B86" s="8">
+        <v>2</v>
+      </c>
+      <c r="C86" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B78" s="8" t="str">
+      <c r="B87" s="8" t="str">
         <f>_xll.qlNonstandardSwapFloatingDayCount(B39)</f>
         <v>Actual/360</v>
       </c>
-      <c r="C78" s="8" t="str">
+      <c r="C87" s="8" t="str">
         <f>_xll.qlNonstandardSwapFloatingDayCount(C39)</f>
         <v>Actual/360</v>
       </c>
     </row>
-    <row r="79" spans="1:3" s="15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="35" t="s">
+    <row r="88" spans="1:3" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="B79" s="36" t="str">
+      <c r="B88" s="36" t="str">
         <f>_xll.qlNonstandardSwapPaymentConvention(B39)</f>
         <v>FOLLOWING</v>
       </c>
-      <c r="C79" s="36" t="str">
+      <c r="C88" s="36" t="str">
         <f>_xll.qlNonstandardSwapPaymentConvention(C39)</f>
         <v>UNADJUSTED</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B80" s="8" t="str">
+      <c r="B89" s="8" t="str">
         <f>_xll.qlNonstandardSwapFixedLeg(B39)</f>
-        <v>欣[test_swap.xlsx]NonStandardSwap!R80C2CashFlow,A</v>
-      </c>
-      <c r="C80" s="8" t="str">
+        <v>欣[test_swap.xlsx]NonStandardSwap!R89C2CashFlow,A</v>
+      </c>
+      <c r="C89" s="8" t="str">
         <f>_xll.qlNonstandardSwapFixedLeg(C39)</f>
-        <v>欣[test_swap.xlsx]NonStandardSwap!R80C3CashFlow,A</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
+        <v>欣[test_swap.xlsx]NonStandardSwap!R89C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B81" s="8" t="str">
+      <c r="B90" s="8" t="str">
         <f>_xll.qlNonstandardSwapFloatingLeg(B39)</f>
-        <v>欣[test_swap.xlsx]NonStandardSwap!R81C2CashFlow,A</v>
-      </c>
-      <c r="C81" s="8" t="str">
+        <v>欣[test_swap.xlsx]NonStandardSwap!R90C2CashFlow,A</v>
+      </c>
+      <c r="C90" s="8" t="str">
         <f>_xll.qlNonstandardSwapFloatingLeg(C39)</f>
-        <v>欣[test_swap.xlsx]NonStandardSwap!R81C3CashFlow,A</v>
+        <v>欣[test_swap.xlsx]NonStandardSwap!R90C3CashFlow,A</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="A75:A77"/>
-    <mergeCell ref="A60:A62"/>
+  <mergeCells count="5">
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="A57:A59"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7373,11 +7437,11 @@
         <v>66</v>
       </c>
       <c r="B12" s="9" t="str">
-        <f>_xll.qlEuribor("3M",B11)</f>
+        <f>_xll.qlEuribor("3M",B11,B2)</f>
         <v>欣[test_swap.xlsx]AssetSwap!R12C2Euribor,A</v>
       </c>
       <c r="C12" s="9" t="str">
-        <f>_xll.qlEuribor("3M",C11)</f>
+        <f>_xll.qlEuribor("3M",C11,B2)</f>
         <v>欣[test_swap.xlsx]AssetSwap!R12C3Euribor,A</v>
       </c>
     </row>
@@ -7673,8 +7737,8 @@
         <f>_xll.qlSwapNpvDateDiscount(B25,B31)</f>
         <v>1</v>
       </c>
-      <c r="C40" s="9">
-        <f>_xll.qlSwapNpvDateDiscount(C25)</f>
+      <c r="C40" s="44">
+        <f>_xll.qlSwapNpvDateDiscount(C25,C31)</f>
         <v>1</v>
       </c>
     </row>
@@ -7761,7 +7825,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="49" t="s">
         <v>115</v>
       </c>
       <c r="B5" s="9">
@@ -7772,7 +7836,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="41"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="9">
         <v>150</v>
       </c>
@@ -7781,7 +7845,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="41"/>
+      <c r="A7" s="49"/>
       <c r="B7" s="9">
         <v>100</v>
       </c>
@@ -7790,7 +7854,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="49" t="s">
         <v>116</v>
       </c>
       <c r="B8" s="9">
@@ -7801,7 +7865,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="41"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="9">
         <v>150</v>
       </c>
@@ -7810,7 +7874,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="41"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="9">
         <v>100</v>
       </c>
@@ -7904,11 +7968,11 @@
         <v>118</v>
       </c>
       <c r="B18" s="9" t="str">
-        <f>_xll.qlEuribor("12M",B17)</f>
+        <f>_xll.qlEuribor("12M",B17,B2)</f>
         <v>欣[test_swap.xlsx]FloatFloatSwap!R18C2Euribor,A</v>
       </c>
       <c r="C18" s="9" t="str">
-        <f>_xll.qlEuribor("12M",C17)</f>
+        <f>_xll.qlEuribor("12M",C17,B2)</f>
         <v>欣[test_swap.xlsx]FloatFloatSwap!R18C3Euribor,A</v>
       </c>
     </row>
@@ -8009,11 +8073,11 @@
         <v>121</v>
       </c>
       <c r="B27" s="9" t="str">
-        <f>_xll.qlEuribor("12M",B26)</f>
+        <f>_xll.qlEuribor("12M",B26,B2)</f>
         <v>欣[test_swap.xlsx]FloatFloatSwap!R27C2Euribor,A</v>
       </c>
       <c r="C27" s="9" t="str">
-        <f>_xll.qlEuribor("12M",C26)</f>
+        <f>_xll.qlEuribor("12M",C26,B2)</f>
         <v>欣[test_swap.xlsx]FloatFloatSwap!R27C3Euribor,A</v>
       </c>
     </row>
@@ -8045,7 +8109,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="41" t="s">
+      <c r="A31" s="49" t="s">
         <v>123</v>
       </c>
       <c r="C31" s="9">
@@ -8053,19 +8117,19 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="41"/>
+      <c r="A32" s="49"/>
       <c r="C32" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="41"/>
+      <c r="A33" s="49"/>
       <c r="C33" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="49" t="s">
         <v>124</v>
       </c>
       <c r="C34" s="9">
@@ -8073,41 +8137,41 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="41"/>
+      <c r="A35" s="49"/>
       <c r="C35" s="9">
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="41"/>
+      <c r="A36" s="49"/>
       <c r="C36" s="9">
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="45" t="s">
+      <c r="A37" s="52" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="45"/>
+      <c r="A38" s="52"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="45"/>
+      <c r="A39" s="52"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="45" t="s">
+      <c r="A40" s="52" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="45"/>
+      <c r="A41" s="52"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="45"/>
+      <c r="A42" s="52"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="41" t="s">
+      <c r="A43" s="49" t="s">
         <v>127</v>
       </c>
       <c r="C43" s="9">
@@ -8115,19 +8179,19 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="41"/>
+      <c r="A44" s="49"/>
       <c r="C44" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="41"/>
+      <c r="A45" s="49"/>
       <c r="C45" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="41" t="s">
+      <c r="A46" s="49" t="s">
         <v>128</v>
       </c>
       <c r="C46" s="9">
@@ -8135,38 +8199,38 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="41"/>
+      <c r="A47" s="49"/>
       <c r="C47" s="9">
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="41"/>
+      <c r="A48" s="49"/>
       <c r="C48" s="9">
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="45" t="s">
+      <c r="A49" s="52" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="45"/>
+      <c r="A50" s="52"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="45"/>
+      <c r="A51" s="52"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="45" t="s">
+      <c r="A52" s="52" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="45"/>
+      <c r="A53" s="52"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="45"/>
+      <c r="A54" s="52"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
@@ -9067,31 +9131,13 @@
       <c r="A59" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B59" s="34" t="str">
-        <f>_xll.qlFixedVsFloatingSwapFloatingDayCount(B25)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no day counter implementation provided
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\daycounters.py", line 58, in xDayCounter
-    return daycounter.name()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 3668, in name
-    return _QuantLib.DayCounter_name(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: no day counter implementation provided
-</v>
-      </c>
-      <c r="C59" s="34" t="str">
-        <f>_xll.qlFixedVsFloatingSwapFloatingDayCount(C25)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no day counter implementation provided
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\daycounters.py", line 58, in xDayCounter
-    return daycounter.name()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 3668, in name
-    return _QuantLib.DayCounter_name(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: no day counter implementation provided
-</v>
+      <c r="B59" s="43">
+        <f>FIND("RuntimeError: RuntimeError: no day counter implementation provided",_xll.qlFixedVsFloatingSwapFloatingDayCount(B25))</f>
+        <v>1</v>
+      </c>
+      <c r="C59" s="43">
+        <f>FIND("RuntimeError: RuntimeError: no day counter implementation provided",_xll.qlFixedVsFloatingSwapFloatingDayCount(C25))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -9235,7 +9281,7 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="41" t="s">
+      <c r="A74" s="49" t="s">
         <v>156</v>
       </c>
       <c r="B74" s="9">
@@ -9246,7 +9292,7 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="41"/>
+      <c r="A75" s="49"/>
       <c r="B75" s="9">
         <v>100</v>
       </c>
@@ -9255,7 +9301,7 @@
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="41"/>
+      <c r="A76" s="49"/>
       <c r="B76" s="9">
         <v>100</v>
       </c>
@@ -9354,7 +9400,7 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="41" t="s">
+      <c r="A85" s="49" t="s">
         <v>157</v>
       </c>
       <c r="B85" s="9">
@@ -9365,7 +9411,7 @@
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="41"/>
+      <c r="A86" s="49"/>
       <c r="B86" s="9">
         <v>100</v>
       </c>
@@ -9374,7 +9420,7 @@
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="41"/>
+      <c r="A87" s="49"/>
       <c r="B87" s="9">
         <v>100</v>
       </c>
@@ -9995,31 +10041,13 @@
       <c r="A139" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B139" s="34" t="str">
-        <f>_xll.qlFixedVsFloatingSwapFloatingDayCount(B105)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no day counter implementation provided
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\daycounters.py", line 58, in xDayCounter
-    return daycounter.name()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 3668, in name
-    return _QuantLib.DayCounter_name(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: no day counter implementation provided
-</v>
-      </c>
-      <c r="C139" s="34" t="str">
-        <f>_xll.qlFixedVsFloatingSwapFloatingDayCount(C105)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no day counter implementation provided
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\daycounters.py", line 58, in xDayCounter
-    return daycounter.name()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 3668, in name
-    return _QuantLib.DayCounter_name(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: no day counter implementation provided
-</v>
+      <c r="B139" s="43">
+        <f xml:space="preserve"> FIND("RuntimeError: RuntimeError: no day counter implementation provided",_xll.qlFixedVsFloatingSwapFloatingDayCount(B105))</f>
+        <v>1</v>
+      </c>
+      <c r="C139" s="43">
+        <f xml:space="preserve"> FIND("RuntimeError: RuntimeError: no day counter implementation provided",_xll.qlFixedVsFloatingSwapFloatingDayCount(C105))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
@@ -10948,31 +10976,13 @@
       <c r="A78" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B78" s="34" t="str">
-        <f>_xll.qlFixedVsFloatingSwapFloatingDayCount(B44)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no day counter implementation provided
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\daycounters.py", line 58, in xDayCounter
-    return daycounter.name()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 3668, in name
-    return _QuantLib.DayCounter_name(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: no day counter implementation provided
-</v>
-      </c>
-      <c r="C78" s="34" t="str">
-        <f>_xll.qlFixedVsFloatingSwapFloatingDayCount(C44)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no day counter implementation provided
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\daycounters.py", line 58, in xDayCounter
-    return daycounter.name()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 3668, in name
-    return _QuantLib.DayCounter_name(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: no day counter implementation provided
-</v>
+      <c r="B78" s="45">
+        <f xml:space="preserve"> FIND("RuntimeError: RuntimeError: no day counter implementation provided",_xll.qlFixedVsFloatingSwapFloatingDayCount(B44))</f>
+        <v>1</v>
+      </c>
+      <c r="C78" s="45">
+        <f xml:space="preserve"> FIND("RuntimeError: RuntimeError: no day counter implementation provided",_xll.qlFixedVsFloatingSwapFloatingDayCount(C44))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">

--- a/tests/workbooktests/workbooks/test_swap.xlsx
+++ b/tests/workbooktests/workbooks/test_swap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939CAC17-0599-4E39-975F-6DA80627BBD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B590A8FD-8E62-4B19-95B6-F4408ADDF59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3885" yWindow="-18240" windowWidth="30690" windowHeight="16530" activeTab="1" xr2:uid="{A576409D-E527-4FE8-BADF-F8DE357B9837}"/>
+    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{A576409D-E527-4FE8-BADF-F8DE357B9837}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabs" sheetId="1" r:id="rId1"/>
@@ -5664,9 +5664,6 @@
       <c r="A12" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="11">
-        <v>2</v>
-      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -5897,8 +5894,8 @@
         <v>欣[test_swap.xlsx]MakeVanillaSwap!R40C2VanillaSwap,A</v>
       </c>
       <c r="C40" s="11" t="str">
-        <f>_xll.qlMakeVanillaSwap(C4,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34,C35,C36,C37,C38,C39)</f>
-        <v>欣[test_swap.xlsx]MakeVanillaSwap!R40C3VanillaSwap,A</v>
+        <f>_xll.qlMakeVanillaSwap(C4,C6,C7,C8,C9,C10,C11,,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34,C35,C36,C37,C38,C39)</f>
+        <v>欣[test_swap.xlsx]MakeVanillaSwap!R40C3VanillaSwap,E</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -8432,16 +8429,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="A8:A10"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="A34:A36"/>
     <mergeCell ref="A37:A39"/>
     <mergeCell ref="A40:A42"/>
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="A8:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10284,9 +10281,6 @@
       <c r="A12" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="11">
-        <v>2</v>
-      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -10551,8 +10545,8 @@
         <v>欣[test_swap.xlsx]MakeOIS!R44C2OvernightIndexedSwap,A</v>
       </c>
       <c r="C44" s="11" t="str">
-        <f>_xll.qlMakeOIS(C4,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34,C35,C36,C37,C38,C39,C40,C41,C42,C43)</f>
-        <v>欣[test_swap.xlsx]MakeOIS!R44C3OvernightIndexedSwap,A</v>
+        <f>_xll.qlMakeOIS(C4,C6,C7,C8,C9,C10,C11,,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34,C35,C36,C37,C38,C39,C40,C41,C42,C43)</f>
+        <v>欣[test_swap.xlsx]MakeOIS!R44C3OvernightIndexedSwap,E</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
